--- a/development/service-ops-api/src/main/resources/templates/excel/vehicles-template.xlsx
+++ b/development/service-ops-api/src/main/resources/templates/excel/vehicles-template.xlsx
@@ -498,13 +498,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -538,6 +539,12 @@
 (선택, 15자리)</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>단말기 ID
+(terminalID)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -560,6 +567,11 @@
           <t>123456789012345</t>
         </is>
       </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>T0001</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -3573,7 +3585,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/development/service-ops-api/src/main/resources/templates/excel/vehicles-template.xlsx
+++ b/development/service-ops-api/src/main/resources/templates/excel/vehicles-template.xlsx
@@ -9,9 +9,16 @@
   <sheets>
     <sheet name="차량 등록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+  <si>
+    <t>관리구분 (삭제 시 '삭제' 입력)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -498,14 +505,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E500"/>
+  <dimension ref="A1:F500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" customWidth="true" width="16.0"/>
+    <col min="2" max="2" customWidth="true" width="14.0"/>
+    <col min="3" max="3" customWidth="true" width="14.0"/>
+    <col min="4" max="4" customWidth="true" width="20.0"/>
+    <col min="5" max="5" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -514,6 +521,7 @@
           <t>※ 필수(*) 항목을 모두 입력하세요. 차량번호 형식: 숫자+한글+숫자 (예: 12가3456). IMEI는 단말기 부착 시 입력하세요.</t>
         </is>
       </c>
+      <c r="F1" s="0"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -545,6 +553,9 @@
 (terminalID)</t>
         </is>
       </c>
+      <c r="F2" t="s" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">

--- a/development/service-ops-api/src/main/resources/templates/excel/vehicles-template.xlsx
+++ b/development/service-ops-api/src/main/resources/templates/excel/vehicles-template.xlsx
@@ -9,16 +9,9 @@
   <sheets>
     <sheet name="차량 등록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
-  <si>
-    <t>관리구분 (삭제 시 '삭제' 입력)</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -505,14 +498,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F500"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="16.0"/>
-    <col min="2" max="2" customWidth="true" width="14.0"/>
-    <col min="3" max="3" customWidth="true" width="14.0"/>
-    <col min="4" max="4" customWidth="true" width="20.0"/>
-    <col min="5" max="5" customWidth="true" width="20.0"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -521,7 +514,6 @@
           <t>※ 필수(*) 항목을 모두 입력하세요. 차량번호 형식: 숫자+한글+숫자 (예: 12가3456). IMEI는 단말기 부착 시 입력하세요.</t>
         </is>
       </c>
-      <c r="F1" s="0"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -553,9 +545,6 @@
 (terminalID)</t>
         </is>
       </c>
-      <c r="F2" t="s" s="0">
-        <v>0</v>
-      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
